--- a/myapp/data_idx_gabung.xlsx
+++ b/myapp/data_idx_gabung.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT APLIKASI SHINY IDX 2026\SHINY FOR IDX\myapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74AEF7CD-831F-46B2-82C0-2D69411273FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE6B80DE-22AE-468B-83FC-1F6766C08F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="506">
   <si>
     <t>No</t>
   </si>
@@ -83,6 +83,51 @@
   </si>
   <si>
     <t>Journal Information</t>
+  </si>
+  <si>
+    <t>Sustainability Report Disclosure On Tax Aggressiveness: Does Company Reputation Matter?</t>
+  </si>
+  <si>
+    <t>Siti Nur Aini, Iman Harymawan, Mohammad Nasih</t>
+  </si>
+  <si>
+    <t>Quality - Access to Success</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.47750/QAS/26.209.17</t>
+  </si>
+  <si>
+    <t>Sustainability Report Disclosure; Corporate Reputation; Tax Aggressiveness</t>
+  </si>
+  <si>
+    <t>STATA</t>
+  </si>
+  <si>
+    <t>This study uses non-financial companies listed on the Indonesia Stock Exchange (IDX) from 2010 to 2019 by using Moderated Regression Analysis (MRA) with a cluster by the firm in Stata 17.0 to predict the relationship between SR disclosure, tax aggressiveness, and company reputation</t>
+  </si>
+  <si>
+    <t>moderated regression analysis</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=17700156709&amp;tip=sid</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/17700156709</t>
+  </si>
+  <si>
+    <t>Management of Optimal Portfolio of Idx Stock Using Single Index Model, Stochastic Dominance, And Almost Stochastic Dominance</t>
+  </si>
+  <si>
+    <t>Isnandar Slamet, Mahaliel G Rimbawan, Yuliana Susanti</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.47750/QAS/26.209.18</t>
+  </si>
+  <si>
+    <t>An optimal portfolio; single index model; stochastic dominance; almost stochastic dominance</t>
+  </si>
+  <si>
+    <t>The methodology used is a case study using monthly closing price data of the ten most active stocks by trading value of IDX stock in 2022 obtained from idx.co.id.</t>
   </si>
   <si>
     <t>Analyzing the nexus of stock return dynamics, trading volume and volatility in the Indian Stock Exchange</t>
@@ -282,9 +327,6 @@
     <t>https://sinta.kemdiktisaintek.go.id/journals/profile/214</t>
   </si>
   <si>
-    <t>STATA</t>
-  </si>
-  <si>
     <t>This study examines the effects of algorithmic trading and financial engineering strategies on stock market volatility in Indonesia, as well as how their interaction influences price stability. A quantitative approach is employed using volatility estimation through the GARCH (1, 1)-M model and dynamic panel regression based on the Generalized Method of Moments (GMM). The data were obtained from 40 LQ45 stocks with daily frequency throughout 2024, using indicators of algorithmic trading intensity (order-to-trade ratio) and financial engineering (derivatives contract volume). The results show that both algorithmic trading and financial engineering have a positive and significant impact on market volatility. 
 Stage 3: panel regression with the Generalized Method of Moments (GMM) approach. GMM is a very flexible and powerful moment-based estimation technique, especially in empirical economic analysis involving instruments and data conditions that are not ideal for classical methods. We use STATA 17 in implementing GMM.
 Market Volatility (Y); Algorithmic Trading (X1); Financial Engineering (X2)</t>
@@ -970,9 +1012,6 @@
     <t>Firm value illustrates how investors and the market view the company's ability to effectively manage its resources effectively. There are several factors that influence firm value, including financial performance, ESG, and firm size. This research aims to assess the impact of financial performance, ESG, and firm size on firm value, along with the role of firm size in influencing the relationship between financial performance and ESG on firm value. The analytical approach employed in this research is moderated regression analysis (MRA). The sample for this research includes firms engaged in the coal sector that are listed on the Indonesian Stock Exchange (IDX) from 2021 to 2023. Based on purposive sampling, 16 companies were selected.</t>
   </si>
   <si>
-    <t>moderated regression analysis</t>
-  </si>
-  <si>
     <t>return on asset; liquidity; financial performance; esg disclosure; leverage; debt to equity ratio; firm size; firm value</t>
   </si>
   <si>
@@ -1057,6 +1096,63 @@
 IDR 1.750.000,00
 Per Article
 Link: https://goodwoodpub.com/index.php/ijfam/about/aboutJournal</t>
+  </si>
+  <si>
+    <t>The Effect of Greenwashing on Firm Performance with Multiple Directorships as Moderating Variable</t>
+  </si>
+  <si>
+    <t>Arista Febri Eriyawan; Cynthia Afriani Utama</t>
+  </si>
+  <si>
+    <t>APTISI Transactions on Technopreneurship</t>
+  </si>
+  <si>
+    <t>2656-8888</t>
+  </si>
+  <si>
+    <t>https://att.aptisi.or.id/index.php/att/article/view/606</t>
+  </si>
+  <si>
+    <t>Firm Performance; Greenwashing; Multiple Directorships; Environmental Performance; ROA</t>
+  </si>
+  <si>
+    <t>Greenwashing, defined as the dissemination of misleading environmental information, has been shown to adversely affect firm performance, particularly in terms of profitability and long-term sustainability. Using data from companies listed on the Indonesia Stock Exchange (IDX) from 2018 to 2022, the study employs panel data analysis to examine the relationship between greenwashing, firm performance, and the influence of multiple directorships.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21101196736&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21101196736</t>
+  </si>
+  <si>
+    <t>Study of Comparison of Stock Performance Before And After Doing Split Stock In Go Public Companies That Are Listing on The Idx Period 2013 – 2015</t>
+  </si>
+  <si>
+    <t>R.A. Norromadani Yuniati, Mirza Safitri Agatha Putri, Latof Syeikhur Rabbani</t>
+  </si>
+  <si>
+    <t>https://att.aptisi.or.id/index.php/att/article/view/48</t>
+  </si>
+  <si>
+    <t>abnormal return; security return variability; trading volume activity; stock split</t>
+  </si>
+  <si>
+    <t>This study aims to determine the difference in abnormal return, trading volume activity, and security return variability before and after the stock split announcement on companies listed on the Indonesia Stock Exchange for the period 2013 - 2015.</t>
+  </si>
+  <si>
+    <t>Differences In Intrinsic Value With Stock Market Prices Using The Price Earning Ratio (Per) Approach As An Investment Decision Making Indicator (Case Study Of Manufacturing Companies In Indonesia Period 2016 - 2017)</t>
+  </si>
+  <si>
+    <t>Ardy Indra Lekso Wibowo; Aditya Dwiansyah Putra; Murni Sari Dewi; Denny Oktaviana Radianto</t>
+  </si>
+  <si>
+    <t>https://att.aptisi.or.id/index.php/att/article/view/23</t>
+  </si>
+  <si>
+    <t>Intrinsic Value; Investment Decision; Price Earning Ratio</t>
+  </si>
+  <si>
+    <t>The samples to be taken in this research are manufacturing companies in Indonesia which are listed on the Indonesia Stock Exchange (IDX) for the period 2016 - 2017 with certain criteria. The results of this research will show that the shares of companies listed are in overvalued, undervalued or correctly valued conditions. So investors can decide to buy, hold or sell their shares.</t>
   </si>
   <si>
     <t>Beyond stability: Mapping financial performance volatility and audit quality</t>
@@ -1597,8 +1693,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:U43" totalsRowShown="0">
-  <autoFilter ref="A1:U43" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:U48" totalsRowShown="0">
+  <autoFilter ref="A1:U48" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Title of Article"/>
@@ -1905,7 +2001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U43"/>
+  <dimension ref="A1:U48"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
@@ -1986,41 +2082,38 @@
       <c r="D2">
         <v>2025</v>
       </c>
+      <c r="E2">
+        <v>26</v>
+      </c>
+      <c r="F2">
+        <v>209</v>
+      </c>
       <c r="G2" t="s">
         <v>23</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>24</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>25</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>26</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>27</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>28</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" t="s">
         <v>29</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>30</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" t="s">
-        <v>32</v>
-      </c>
-      <c r="S2" t="s">
-        <v>33</v>
-      </c>
-      <c r="T2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -2028,55 +2121,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3">
+        <v>2025</v>
+      </c>
+      <c r="E3">
+        <v>26</v>
+      </c>
+      <c r="F3">
+        <v>209</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" t="s">
         <v>35</v>
       </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3">
-        <v>2022</v>
-      </c>
-      <c r="E3">
-        <v>12</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" t="s">
-        <v>43</v>
-      </c>
-      <c r="N3" t="s">
-        <v>44</v>
-      </c>
-      <c r="O3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T3" t="s">
-        <v>47</v>
-      </c>
-      <c r="U3" t="s">
-        <v>48</v>
+      <c r="Q3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -2084,49 +2159,49 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4">
+        <v>2025</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O4" t="s">
+        <v>44</v>
+      </c>
+      <c r="P4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T4" t="s">
         <v>49</v>
-      </c>
-      <c r="C4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4">
-        <v>2026</v>
-      </c>
-      <c r="G4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J4" t="s">
-        <v>54</v>
-      </c>
-      <c r="N4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O4" t="s">
-        <v>56</v>
-      </c>
-      <c r="P4" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>58</v>
-      </c>
-      <c r="R4" t="s">
-        <v>59</v>
-      </c>
-      <c r="S4" t="s">
-        <v>33</v>
-      </c>
-      <c r="T4" t="s">
-        <v>60</v>
-      </c>
-      <c r="U4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -2134,55 +2209,55 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D5">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E5">
         <v>12</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H5" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="I5" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="J5" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="L5" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="M5" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="N5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="O5" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P5" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="T5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="U5" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -2190,55 +2265,49 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6">
+        <v>2026</v>
+      </c>
+      <c r="G6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6" t="s">
+        <v>69</v>
+      </c>
+      <c r="N6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" t="s">
+        <v>71</v>
+      </c>
+      <c r="P6" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q6" t="s">
         <v>73</v>
       </c>
-      <c r="C6" t="s">
+      <c r="R6" t="s">
         <v>74</v>
       </c>
-      <c r="D6">
-        <v>2025</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="S6" t="s">
+        <v>48</v>
+      </c>
+      <c r="T6" t="s">
         <v>75</v>
       </c>
-      <c r="H6" t="s">
+      <c r="U6" t="s">
         <v>76</v>
-      </c>
-      <c r="I6" t="s">
-        <v>77</v>
-      </c>
-      <c r="J6" t="s">
-        <v>78</v>
-      </c>
-      <c r="K6" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" t="s">
-        <v>79</v>
-      </c>
-      <c r="M6" t="s">
-        <v>80</v>
-      </c>
-      <c r="N6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O6" t="s">
-        <v>82</v>
-      </c>
-      <c r="P6" t="s">
-        <v>83</v>
-      </c>
-      <c r="T6" t="s">
-        <v>84</v>
-      </c>
-      <c r="U6" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -2246,55 +2315,55 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7">
+        <v>2023</v>
+      </c>
+      <c r="E7">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" t="s">
+        <v>83</v>
+      </c>
+      <c r="M7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7" t="s">
+        <v>84</v>
+      </c>
+      <c r="O7" t="s">
+        <v>85</v>
+      </c>
+      <c r="P7" t="s">
+        <v>84</v>
+      </c>
+      <c r="T7" t="s">
         <v>86</v>
       </c>
-      <c r="C7" t="s">
+      <c r="U7" t="s">
         <v>87</v>
-      </c>
-      <c r="D7">
-        <v>2025</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I7" t="s">
-        <v>88</v>
-      </c>
-      <c r="J7" t="s">
-        <v>89</v>
-      </c>
-      <c r="K7" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" t="s">
-        <v>79</v>
-      </c>
-      <c r="M7" t="s">
-        <v>80</v>
-      </c>
-      <c r="N7" t="s">
-        <v>90</v>
-      </c>
-      <c r="O7" t="s">
-        <v>45</v>
-      </c>
-      <c r="P7" t="s">
-        <v>91</v>
-      </c>
-      <c r="T7" t="s">
-        <v>92</v>
-      </c>
-      <c r="U7" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -2302,55 +2371,55 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J8" t="s">
+        <v>93</v>
+      </c>
+      <c r="K8" t="s">
+        <v>56</v>
+      </c>
+      <c r="L8" t="s">
+        <v>94</v>
+      </c>
+      <c r="M8" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" t="s">
         <v>95</v>
       </c>
-      <c r="H8" t="s">
+      <c r="O8" t="s">
         <v>96</v>
       </c>
-      <c r="I8" t="s">
+      <c r="P8" t="s">
         <v>97</v>
       </c>
-      <c r="J8" t="s">
+      <c r="T8" t="s">
         <v>98</v>
       </c>
-      <c r="K8" t="s">
+      <c r="U8" t="s">
         <v>99</v>
-      </c>
-      <c r="L8" t="s">
-        <v>100</v>
-      </c>
-      <c r="M8" t="s">
-        <v>101</v>
-      </c>
-      <c r="N8" t="s">
-        <v>102</v>
-      </c>
-      <c r="O8" t="s">
-        <v>45</v>
-      </c>
-      <c r="P8" t="s">
-        <v>103</v>
-      </c>
-      <c r="T8" t="s">
-        <v>104</v>
-      </c>
-      <c r="U8" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -2358,55 +2427,55 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D9">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E9">
         <v>10</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="J9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="K9" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" t="s">
+        <v>94</v>
+      </c>
+      <c r="M9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" t="s">
+        <v>104</v>
+      </c>
+      <c r="O9" t="s">
+        <v>60</v>
+      </c>
+      <c r="P9" t="s">
+        <v>105</v>
+      </c>
+      <c r="T9" t="s">
+        <v>106</v>
+      </c>
+      <c r="U9" t="s">
         <v>99</v>
-      </c>
-      <c r="L9" t="s">
-        <v>112</v>
-      </c>
-      <c r="M9" t="s">
-        <v>43</v>
-      </c>
-      <c r="N9" t="s">
-        <v>113</v>
-      </c>
-      <c r="O9" t="s">
-        <v>114</v>
-      </c>
-      <c r="P9" t="s">
-        <v>113</v>
-      </c>
-      <c r="T9" t="s">
-        <v>115</v>
-      </c>
-      <c r="U9" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -2414,55 +2483,55 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" t="s">
+        <v>110</v>
+      </c>
+      <c r="I10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J10" t="s">
+        <v>112</v>
+      </c>
+      <c r="K10" t="s">
+        <v>113</v>
+      </c>
+      <c r="L10" t="s">
+        <v>114</v>
+      </c>
+      <c r="M10" t="s">
+        <v>115</v>
+      </c>
+      <c r="N10" t="s">
+        <v>116</v>
+      </c>
+      <c r="O10" t="s">
+        <v>60</v>
+      </c>
+      <c r="P10" t="s">
+        <v>117</v>
+      </c>
+      <c r="T10" t="s">
+        <v>118</v>
+      </c>
+      <c r="U10" t="s">
         <v>119</v>
-      </c>
-      <c r="H10" t="s">
-        <v>120</v>
-      </c>
-      <c r="I10" t="s">
-        <v>121</v>
-      </c>
-      <c r="J10" t="s">
-        <v>122</v>
-      </c>
-      <c r="K10" t="s">
-        <v>99</v>
-      </c>
-      <c r="L10" t="s">
-        <v>123</v>
-      </c>
-      <c r="M10" t="s">
-        <v>124</v>
-      </c>
-      <c r="N10" t="s">
-        <v>125</v>
-      </c>
-      <c r="O10" t="s">
-        <v>126</v>
-      </c>
-      <c r="P10" t="s">
-        <v>125</v>
-      </c>
-      <c r="T10" t="s">
-        <v>127</v>
-      </c>
-      <c r="U10" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -2470,55 +2539,55 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C11" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D11">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H11" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I11" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K11" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="L11" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M11" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="N11" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="O11" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="P11" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="T11" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="U11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -2526,10 +2595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D12">
         <v>2025</v>
@@ -2538,43 +2607,43 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="s">
+        <v>133</v>
+      </c>
+      <c r="H12" t="s">
+        <v>134</v>
+      </c>
+      <c r="I12" t="s">
+        <v>135</v>
+      </c>
+      <c r="J12" t="s">
+        <v>136</v>
+      </c>
+      <c r="K12" t="s">
+        <v>113</v>
+      </c>
+      <c r="L12" t="s">
+        <v>137</v>
+      </c>
+      <c r="M12" t="s">
         <v>138</v>
       </c>
-      <c r="H12" t="s">
+      <c r="N12" t="s">
         <v>139</v>
       </c>
-      <c r="I12" t="s">
+      <c r="O12" t="s">
         <v>140</v>
       </c>
-      <c r="J12" t="s">
+      <c r="P12" t="s">
+        <v>139</v>
+      </c>
+      <c r="T12" t="s">
         <v>141</v>
       </c>
-      <c r="K12" t="s">
+      <c r="U12" t="s">
         <v>142</v>
-      </c>
-      <c r="L12" t="s">
-        <v>143</v>
-      </c>
-      <c r="M12" t="s">
-        <v>27</v>
-      </c>
-      <c r="N12" t="s">
-        <v>144</v>
-      </c>
-      <c r="O12" t="s">
-        <v>145</v>
-      </c>
-      <c r="P12" t="s">
-        <v>146</v>
-      </c>
-      <c r="T12" t="s">
-        <v>147</v>
-      </c>
-      <c r="U12" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -2582,55 +2651,55 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C13" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="H13" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="I13" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="J13" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="K13" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="L13" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="M13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N13" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="O13" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="P13" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="T13" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="U13" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -2638,55 +2707,55 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C14" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="D14">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="H14" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="I14" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="J14" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="K14" t="s">
-        <v>41</v>
+        <v>156</v>
       </c>
       <c r="L14" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="M14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N14" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="O14" t="s">
-        <v>45</v>
+        <v>159</v>
       </c>
       <c r="P14" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="T14" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="U14" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -2694,55 +2763,55 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C15" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D15">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" t="s">
+        <v>165</v>
+      </c>
+      <c r="H15" t="s">
+        <v>166</v>
+      </c>
+      <c r="I15" t="s">
+        <v>167</v>
+      </c>
+      <c r="J15" t="s">
+        <v>168</v>
+      </c>
+      <c r="K15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" t="s">
+        <v>169</v>
+      </c>
+      <c r="M15" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" t="s">
+        <v>170</v>
+      </c>
+      <c r="O15" t="s">
+        <v>171</v>
+      </c>
+      <c r="P15" t="s">
+        <v>172</v>
+      </c>
+      <c r="T15" t="s">
         <v>173</v>
       </c>
-      <c r="H15" t="s">
+      <c r="U15" t="s">
         <v>174</v>
-      </c>
-      <c r="I15" t="s">
-        <v>175</v>
-      </c>
-      <c r="J15" t="s">
-        <v>176</v>
-      </c>
-      <c r="K15" t="s">
-        <v>99</v>
-      </c>
-      <c r="L15" t="s">
-        <v>177</v>
-      </c>
-      <c r="M15" t="s">
-        <v>43</v>
-      </c>
-      <c r="N15" t="s">
-        <v>178</v>
-      </c>
-      <c r="O15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P15" t="s">
-        <v>179</v>
-      </c>
-      <c r="T15" t="s">
-        <v>180</v>
-      </c>
-      <c r="U15" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -2750,55 +2819,55 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>175</v>
+      </c>
+      <c r="C16" t="s">
+        <v>176</v>
+      </c>
+      <c r="D16">
+        <v>2021</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H16" t="s">
+        <v>178</v>
+      </c>
+      <c r="I16" t="s">
+        <v>179</v>
+      </c>
+      <c r="J16" t="s">
+        <v>180</v>
+      </c>
+      <c r="K16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" t="s">
+        <v>181</v>
+      </c>
+      <c r="M16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N16" t="s">
         <v>182</v>
       </c>
-      <c r="C16" t="s">
+      <c r="O16" t="s">
+        <v>60</v>
+      </c>
+      <c r="P16" t="s">
+        <v>182</v>
+      </c>
+      <c r="T16" t="s">
         <v>183</v>
       </c>
-      <c r="D16">
-        <v>2025</v>
-      </c>
-      <c r="E16">
-        <v>8</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="U16" t="s">
         <v>184</v>
-      </c>
-      <c r="H16" t="s">
-        <v>185</v>
-      </c>
-      <c r="I16" t="s">
-        <v>186</v>
-      </c>
-      <c r="J16" t="s">
-        <v>187</v>
-      </c>
-      <c r="K16" t="s">
-        <v>41</v>
-      </c>
-      <c r="L16" t="s">
-        <v>188</v>
-      </c>
-      <c r="M16" t="s">
-        <v>80</v>
-      </c>
-      <c r="N16" t="s">
-        <v>189</v>
-      </c>
-      <c r="O16" t="s">
-        <v>190</v>
-      </c>
-      <c r="P16" t="s">
-        <v>191</v>
-      </c>
-      <c r="T16" t="s">
-        <v>192</v>
-      </c>
-      <c r="U16" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -2806,55 +2875,55 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17">
+        <v>2021</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>187</v>
+      </c>
+      <c r="H17" t="s">
+        <v>188</v>
+      </c>
+      <c r="I17" t="s">
+        <v>189</v>
+      </c>
+      <c r="J17" t="s">
+        <v>190</v>
+      </c>
+      <c r="K17" t="s">
+        <v>113</v>
+      </c>
+      <c r="L17" t="s">
+        <v>191</v>
+      </c>
+      <c r="M17" t="s">
+        <v>58</v>
+      </c>
+      <c r="N17" t="s">
+        <v>192</v>
+      </c>
+      <c r="O17" t="s">
+        <v>85</v>
+      </c>
+      <c r="P17" t="s">
+        <v>193</v>
+      </c>
+      <c r="T17" t="s">
         <v>194</v>
       </c>
-      <c r="C17" t="s">
+      <c r="U17" t="s">
         <v>195</v>
-      </c>
-      <c r="D17">
-        <v>2025</v>
-      </c>
-      <c r="E17">
-        <v>8</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17" t="s">
-        <v>196</v>
-      </c>
-      <c r="H17" t="s">
-        <v>197</v>
-      </c>
-      <c r="I17" t="s">
-        <v>198</v>
-      </c>
-      <c r="J17" t="s">
-        <v>199</v>
-      </c>
-      <c r="K17" t="s">
-        <v>142</v>
-      </c>
-      <c r="L17" t="s">
-        <v>200</v>
-      </c>
-      <c r="M17" t="s">
-        <v>27</v>
-      </c>
-      <c r="N17" t="s">
-        <v>201</v>
-      </c>
-      <c r="O17" t="s">
-        <v>202</v>
-      </c>
-      <c r="P17" t="s">
-        <v>203</v>
-      </c>
-      <c r="T17" t="s">
-        <v>204</v>
-      </c>
-      <c r="U17" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -2862,49 +2931,55 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C18" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="H18" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="I18" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="J18" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="K18" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="L18" t="s">
-        <v>212</v>
+        <v>202</v>
+      </c>
+      <c r="M18" t="s">
+        <v>26</v>
       </c>
       <c r="N18" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="O18" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="P18" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="T18" t="s">
-        <v>216</v>
+        <v>206</v>
+      </c>
+      <c r="U18" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -2912,55 +2987,55 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>208</v>
+      </c>
+      <c r="C19" t="s">
+        <v>209</v>
+      </c>
+      <c r="D19">
+        <v>2025</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19" t="s">
+        <v>210</v>
+      </c>
+      <c r="H19" t="s">
+        <v>211</v>
+      </c>
+      <c r="I19" t="s">
+        <v>212</v>
+      </c>
+      <c r="J19" t="s">
+        <v>213</v>
+      </c>
+      <c r="K19" t="s">
+        <v>156</v>
+      </c>
+      <c r="L19" t="s">
+        <v>214</v>
+      </c>
+      <c r="M19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N19" t="s">
+        <v>215</v>
+      </c>
+      <c r="O19" t="s">
+        <v>216</v>
+      </c>
+      <c r="P19" t="s">
         <v>217</v>
       </c>
-      <c r="C19" t="s">
+      <c r="T19" t="s">
         <v>218</v>
       </c>
-      <c r="D19">
-        <v>2026</v>
-      </c>
-      <c r="E19">
-        <v>27</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="U19" t="s">
         <v>219</v>
-      </c>
-      <c r="H19" t="s">
-        <v>220</v>
-      </c>
-      <c r="I19" t="s">
-        <v>221</v>
-      </c>
-      <c r="J19" t="s">
-        <v>222</v>
-      </c>
-      <c r="K19" t="s">
-        <v>41</v>
-      </c>
-      <c r="L19" t="s">
-        <v>223</v>
-      </c>
-      <c r="M19" t="s">
-        <v>80</v>
-      </c>
-      <c r="N19" t="s">
-        <v>224</v>
-      </c>
-      <c r="O19" t="s">
-        <v>225</v>
-      </c>
-      <c r="P19" t="s">
-        <v>224</v>
-      </c>
-      <c r="T19" t="s">
-        <v>226</v>
-      </c>
-      <c r="U19" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -2968,55 +3043,49 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C20" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H20" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="I20" t="s">
+        <v>224</v>
+      </c>
+      <c r="J20" t="s">
+        <v>225</v>
+      </c>
+      <c r="K20" t="s">
+        <v>113</v>
+      </c>
+      <c r="L20" t="s">
+        <v>226</v>
+      </c>
+      <c r="N20" t="s">
+        <v>227</v>
+      </c>
+      <c r="O20" t="s">
+        <v>228</v>
+      </c>
+      <c r="P20" t="s">
+        <v>229</v>
+      </c>
+      <c r="T20" t="s">
         <v>230</v>
-      </c>
-      <c r="J20" t="s">
-        <v>231</v>
-      </c>
-      <c r="K20" t="s">
-        <v>41</v>
-      </c>
-      <c r="L20" t="s">
-        <v>223</v>
-      </c>
-      <c r="M20" t="s">
-        <v>232</v>
-      </c>
-      <c r="N20" t="s">
-        <v>233</v>
-      </c>
-      <c r="O20" t="s">
-        <v>225</v>
-      </c>
-      <c r="P20" t="s">
-        <v>234</v>
-      </c>
-      <c r="T20" t="s">
-        <v>235</v>
-      </c>
-      <c r="U20" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -3024,55 +3093,55 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" t="s">
+        <v>232</v>
+      </c>
+      <c r="D21">
+        <v>2026</v>
+      </c>
+      <c r="E21">
+        <v>27</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>233</v>
+      </c>
+      <c r="H21" t="s">
+        <v>234</v>
+      </c>
+      <c r="I21" t="s">
+        <v>235</v>
+      </c>
+      <c r="J21" t="s">
         <v>236</v>
       </c>
-      <c r="C21" t="s">
+      <c r="K21" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" t="s">
         <v>237</v>
       </c>
-      <c r="D21">
-        <v>2024</v>
-      </c>
-      <c r="E21">
-        <v>25</v>
-      </c>
-      <c r="F21">
-        <v>2</v>
-      </c>
-      <c r="G21" t="s">
-        <v>219</v>
-      </c>
-      <c r="H21" t="s">
-        <v>220</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="M21" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" t="s">
         <v>238</v>
       </c>
-      <c r="J21" t="s">
+      <c r="O21" t="s">
         <v>239</v>
       </c>
-      <c r="K21" t="s">
-        <v>41</v>
-      </c>
-      <c r="L21" t="s">
-        <v>223</v>
-      </c>
-      <c r="M21" t="s">
-        <v>43</v>
-      </c>
-      <c r="N21" t="s">
+      <c r="P21" t="s">
+        <v>238</v>
+      </c>
+      <c r="T21" t="s">
         <v>240</v>
       </c>
-      <c r="O21" t="s">
+      <c r="U21" t="s">
         <v>241</v>
-      </c>
-      <c r="P21" t="s">
-        <v>242</v>
-      </c>
-      <c r="T21" t="s">
-        <v>243</v>
-      </c>
-      <c r="U21" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -3080,55 +3149,55 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C22" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D22">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E22">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F22">
         <v>3</v>
       </c>
       <c r="G22" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="H22" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="I22" t="s">
+        <v>244</v>
+      </c>
+      <c r="J22" t="s">
+        <v>245</v>
+      </c>
+      <c r="K22" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" t="s">
+        <v>237</v>
+      </c>
+      <c r="M22" t="s">
         <v>246</v>
       </c>
-      <c r="J22" t="s">
+      <c r="N22" t="s">
         <v>247</v>
       </c>
-      <c r="K22" t="s">
-        <v>41</v>
-      </c>
-      <c r="L22" t="s">
-        <v>223</v>
-      </c>
-      <c r="M22" t="s">
-        <v>124</v>
-      </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
+        <v>239</v>
+      </c>
+      <c r="P22" t="s">
         <v>248</v>
       </c>
-      <c r="O22" t="s">
+      <c r="T22" t="s">
         <v>249</v>
       </c>
-      <c r="P22" t="s">
-        <v>250</v>
-      </c>
-      <c r="T22" t="s">
-        <v>251</v>
-      </c>
       <c r="U22" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -3136,55 +3205,55 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>250</v>
+      </c>
+      <c r="C23" t="s">
+        <v>251</v>
+      </c>
+      <c r="D23">
+        <v>2024</v>
+      </c>
+      <c r="E23">
+        <v>25</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23" t="s">
+        <v>233</v>
+      </c>
+      <c r="H23" t="s">
+        <v>234</v>
+      </c>
+      <c r="I23" t="s">
         <v>252</v>
       </c>
-      <c r="C23" t="s">
+      <c r="J23" t="s">
         <v>253</v>
       </c>
-      <c r="D23">
-        <v>2022</v>
-      </c>
-      <c r="E23">
-        <v>23</v>
-      </c>
-      <c r="F23">
-        <v>3</v>
-      </c>
-      <c r="G23" t="s">
-        <v>219</v>
-      </c>
-      <c r="H23" t="s">
-        <v>220</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="K23" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" t="s">
+        <v>237</v>
+      </c>
+      <c r="M23" t="s">
+        <v>58</v>
+      </c>
+      <c r="N23" t="s">
         <v>254</v>
       </c>
-      <c r="J23" t="s">
+      <c r="O23" t="s">
         <v>255</v>
       </c>
-      <c r="K23" t="s">
-        <v>41</v>
-      </c>
-      <c r="L23" t="s">
-        <v>223</v>
-      </c>
-      <c r="M23" t="s">
-        <v>43</v>
-      </c>
-      <c r="N23" t="s">
+      <c r="P23" t="s">
         <v>256</v>
       </c>
-      <c r="O23" t="s">
+      <c r="T23" t="s">
         <v>257</v>
       </c>
-      <c r="P23" t="s">
-        <v>258</v>
-      </c>
-      <c r="T23" t="s">
-        <v>259</v>
-      </c>
       <c r="U23" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -3192,52 +3261,55 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>258</v>
+      </c>
+      <c r="C24" t="s">
+        <v>259</v>
+      </c>
+      <c r="D24">
+        <v>2023</v>
+      </c>
+      <c r="E24">
+        <v>24</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" t="s">
+        <v>233</v>
+      </c>
+      <c r="H24" t="s">
+        <v>234</v>
+      </c>
+      <c r="I24" t="s">
         <v>260</v>
       </c>
-      <c r="C24" t="s">
+      <c r="J24" t="s">
         <v>261</v>
       </c>
-      <c r="D24">
-        <v>2021</v>
-      </c>
-      <c r="E24">
-        <v>22</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24" t="s">
-        <v>219</v>
-      </c>
-      <c r="H24" t="s">
-        <v>220</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="K24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L24" t="s">
+        <v>237</v>
+      </c>
+      <c r="M24" t="s">
+        <v>138</v>
+      </c>
+      <c r="N24" t="s">
         <v>262</v>
       </c>
-      <c r="J24" t="s">
+      <c r="O24" t="s">
         <v>263</v>
       </c>
-      <c r="K24" t="s">
-        <v>41</v>
-      </c>
-      <c r="L24" t="s">
-        <v>223</v>
-      </c>
-      <c r="N24" t="s">
+      <c r="P24" t="s">
         <v>264</v>
       </c>
-      <c r="O24" t="s">
-        <v>214</v>
-      </c>
-      <c r="P24" t="s">
+      <c r="T24" t="s">
         <v>265</v>
       </c>
-      <c r="T24" t="s">
-        <v>266</v>
-      </c>
       <c r="U24" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3245,55 +3317,55 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>266</v>
+      </c>
+      <c r="C25" t="s">
         <v>267</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25">
+        <v>2022</v>
+      </c>
+      <c r="E25">
+        <v>23</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25" t="s">
+        <v>233</v>
+      </c>
+      <c r="H25" t="s">
+        <v>234</v>
+      </c>
+      <c r="I25" t="s">
         <v>268</v>
       </c>
-      <c r="D25">
-        <v>2020</v>
-      </c>
-      <c r="E25">
-        <v>21</v>
-      </c>
-      <c r="F25">
-        <v>2</v>
-      </c>
-      <c r="G25" t="s">
-        <v>219</v>
-      </c>
-      <c r="H25" t="s">
-        <v>220</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>269</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
+        <v>56</v>
+      </c>
+      <c r="L25" t="s">
+        <v>237</v>
+      </c>
+      <c r="M25" t="s">
+        <v>58</v>
+      </c>
+      <c r="N25" t="s">
         <v>270</v>
       </c>
-      <c r="K25" t="s">
-        <v>41</v>
-      </c>
-      <c r="L25" t="s">
-        <v>223</v>
-      </c>
-      <c r="M25" t="s">
-        <v>43</v>
-      </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
         <v>271</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>272</v>
       </c>
-      <c r="P25" t="s">
+      <c r="T25" t="s">
         <v>273</v>
       </c>
-      <c r="T25" t="s">
-        <v>274</v>
-      </c>
       <c r="U25" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3301,55 +3373,52 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>274</v>
+      </c>
+      <c r="C26" t="s">
         <v>275</v>
       </c>
-      <c r="C26" t="s">
-        <v>276</v>
-      </c>
       <c r="D26">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E26">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" t="s">
+        <v>233</v>
+      </c>
+      <c r="H26" t="s">
+        <v>234</v>
+      </c>
+      <c r="I26" t="s">
+        <v>276</v>
+      </c>
+      <c r="J26" t="s">
         <v>277</v>
       </c>
-      <c r="H26" t="s">
+      <c r="K26" t="s">
+        <v>56</v>
+      </c>
+      <c r="L26" t="s">
+        <v>237</v>
+      </c>
+      <c r="N26" t="s">
         <v>278</v>
       </c>
-      <c r="I26" t="s">
+      <c r="O26" t="s">
+        <v>228</v>
+      </c>
+      <c r="P26" t="s">
         <v>279</v>
-      </c>
-      <c r="J26" t="s">
-        <v>280</v>
-      </c>
-      <c r="K26" t="s">
-        <v>41</v>
-      </c>
-      <c r="L26" t="s">
-        <v>281</v>
-      </c>
-      <c r="M26" t="s">
-        <v>80</v>
-      </c>
-      <c r="N26" t="s">
-        <v>282</v>
-      </c>
-      <c r="O26" t="s">
-        <v>283</v>
-      </c>
-      <c r="P26" t="s">
-        <v>284</v>
       </c>
       <c r="T26" t="s">
         <v>280</v>
       </c>
       <c r="U26" t="s">
-        <v>285</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3357,55 +3426,55 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C27" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D27">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F27">
         <v>2</v>
       </c>
       <c r="G27" t="s">
+        <v>233</v>
+      </c>
+      <c r="H27" t="s">
+        <v>234</v>
+      </c>
+      <c r="I27" t="s">
+        <v>283</v>
+      </c>
+      <c r="J27" t="s">
+        <v>284</v>
+      </c>
+      <c r="K27" t="s">
+        <v>56</v>
+      </c>
+      <c r="L27" t="s">
+        <v>237</v>
+      </c>
+      <c r="M27" t="s">
+        <v>58</v>
+      </c>
+      <c r="N27" t="s">
+        <v>285</v>
+      </c>
+      <c r="O27" t="s">
+        <v>286</v>
+      </c>
+      <c r="P27" t="s">
+        <v>287</v>
+      </c>
+      <c r="T27" t="s">
         <v>288</v>
       </c>
-      <c r="H27" t="s">
-        <v>289</v>
-      </c>
-      <c r="I27" t="s">
-        <v>290</v>
-      </c>
-      <c r="J27" t="s">
-        <v>291</v>
-      </c>
-      <c r="K27" t="s">
-        <v>41</v>
-      </c>
-      <c r="L27" t="s">
-        <v>292</v>
-      </c>
-      <c r="M27" t="s">
-        <v>27</v>
-      </c>
-      <c r="N27" t="s">
-        <v>293</v>
-      </c>
-      <c r="O27" t="s">
-        <v>294</v>
-      </c>
-      <c r="P27" t="s">
-        <v>293</v>
-      </c>
-      <c r="T27" t="s">
-        <v>295</v>
-      </c>
       <c r="U27" t="s">
-        <v>296</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3413,55 +3482,55 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C28" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="D28">
         <v>2025</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" t="s">
+        <v>291</v>
+      </c>
+      <c r="H28" t="s">
+        <v>292</v>
+      </c>
+      <c r="I28" t="s">
+        <v>293</v>
+      </c>
+      <c r="J28" t="s">
+        <v>294</v>
+      </c>
+      <c r="K28" t="s">
+        <v>56</v>
+      </c>
+      <c r="L28" t="s">
+        <v>295</v>
+      </c>
+      <c r="M28" t="s">
+        <v>26</v>
+      </c>
+      <c r="N28" t="s">
+        <v>296</v>
+      </c>
+      <c r="O28" t="s">
+        <v>297</v>
+      </c>
+      <c r="P28" t="s">
+        <v>298</v>
+      </c>
+      <c r="T28" t="s">
+        <v>294</v>
+      </c>
+      <c r="U28" t="s">
         <v>299</v>
-      </c>
-      <c r="H28" t="s">
-        <v>300</v>
-      </c>
-      <c r="I28" t="s">
-        <v>301</v>
-      </c>
-      <c r="J28" t="s">
-        <v>302</v>
-      </c>
-      <c r="K28" t="s">
-        <v>142</v>
-      </c>
-      <c r="L28" t="s">
-        <v>303</v>
-      </c>
-      <c r="M28" t="s">
-        <v>43</v>
-      </c>
-      <c r="N28" t="s">
-        <v>304</v>
-      </c>
-      <c r="O28" t="s">
-        <v>294</v>
-      </c>
-      <c r="P28" t="s">
-        <v>305</v>
-      </c>
-      <c r="T28" t="s">
-        <v>306</v>
-      </c>
-      <c r="U28" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3469,55 +3538,55 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C29" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="D29">
         <v>2025</v>
       </c>
       <c r="E29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="H29" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="I29" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="J29" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="K29" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="L29" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="M29" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="N29" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="O29" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="P29" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="T29" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="U29" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3525,52 +3594,55 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C30" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="D30">
         <v>2025</v>
       </c>
       <c r="E30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="H30" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="I30" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="J30" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="K30" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="L30" t="s">
-        <v>325</v>
+        <v>316</v>
+      </c>
+      <c r="M30" t="s">
+        <v>58</v>
       </c>
       <c r="N30" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="O30" t="s">
-        <v>327</v>
+        <v>28</v>
       </c>
       <c r="P30" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="T30" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="U30" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3578,10 +3650,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="C31" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="D31">
         <v>2025</v>
@@ -3590,43 +3662,43 @@
         <v>7</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="H31" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="I31" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="J31" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="K31" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="L31" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="M31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N31" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="O31" t="s">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="P31" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="T31" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="U31" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3634,55 +3706,40 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="C32" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="D32">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="H32" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="I32" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="J32" t="s">
-        <v>347</v>
-      </c>
-      <c r="K32" t="s">
-        <v>41</v>
-      </c>
-      <c r="L32" t="s">
-        <v>348</v>
-      </c>
-      <c r="M32" t="s">
-        <v>43</v>
-      </c>
-      <c r="N32" t="s">
-        <v>349</v>
-      </c>
-      <c r="O32" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="P32" t="s">
-        <v>349</v>
-      </c>
-      <c r="T32" t="s">
-        <v>351</v>
-      </c>
-      <c r="U32" t="s">
-        <v>352</v>
+        <v>338</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>339</v>
+      </c>
+      <c r="R32" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3690,55 +3747,40 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C33" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="D33">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="E33">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="H33" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="I33" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="J33" t="s">
-        <v>358</v>
-      </c>
-      <c r="K33" t="s">
-        <v>41</v>
-      </c>
-      <c r="L33" t="s">
-        <v>359</v>
-      </c>
-      <c r="M33" t="s">
-        <v>43</v>
-      </c>
-      <c r="N33" t="s">
-        <v>360</v>
-      </c>
-      <c r="O33" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="P33" t="s">
-        <v>360</v>
-      </c>
-      <c r="T33" t="s">
-        <v>362</v>
-      </c>
-      <c r="U33" t="s">
-        <v>363</v>
+        <v>345</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>339</v>
+      </c>
+      <c r="R33" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3746,55 +3788,40 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="C34" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="D34">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="E34">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="H34" t="s">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="I34" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="J34" t="s">
-        <v>369</v>
-      </c>
-      <c r="K34" t="s">
-        <v>99</v>
-      </c>
-      <c r="L34" t="s">
-        <v>370</v>
-      </c>
-      <c r="M34" t="s">
-        <v>27</v>
-      </c>
-      <c r="N34" t="s">
-        <v>371</v>
-      </c>
-      <c r="O34" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="P34" t="s">
-        <v>373</v>
-      </c>
-      <c r="T34" t="s">
-        <v>374</v>
-      </c>
-      <c r="U34" t="s">
-        <v>375</v>
+        <v>350</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>339</v>
+      </c>
+      <c r="R34" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3802,55 +3829,52 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="C35" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="D35">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G35" t="s">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="H35" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="I35" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="J35" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="K35" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="L35" t="s">
-        <v>382</v>
-      </c>
-      <c r="M35" t="s">
-        <v>80</v>
+        <v>357</v>
       </c>
       <c r="N35" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="O35" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="P35" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="T35" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="U35" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3858,55 +3882,55 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="C36" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="D36">
         <v>2025</v>
       </c>
       <c r="E36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36">
         <v>2</v>
       </c>
       <c r="G36" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="H36" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="I36" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="J36" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="K36" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="L36" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="M36" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="N36" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="O36" t="s">
-        <v>396</v>
+        <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="T36" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="U36" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3914,55 +3938,55 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="C37" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="D37">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E37">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
       <c r="H37" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="I37" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="J37" t="s">
-        <v>405</v>
+        <v>379</v>
       </c>
       <c r="K37" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="L37" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="M37" t="s">
-        <v>407</v>
+        <v>58</v>
       </c>
       <c r="N37" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="O37" t="s">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="P37" t="s">
-        <v>350</v>
+        <v>381</v>
       </c>
       <c r="T37" t="s">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="U37" t="s">
-        <v>411</v>
+        <v>384</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -3970,55 +3994,55 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>412</v>
+        <v>385</v>
       </c>
       <c r="C38" t="s">
-        <v>413</v>
+        <v>386</v>
       </c>
       <c r="D38">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>414</v>
+        <v>387</v>
       </c>
       <c r="H38" t="s">
-        <v>415</v>
+        <v>388</v>
       </c>
       <c r="I38" t="s">
-        <v>416</v>
+        <v>389</v>
       </c>
       <c r="J38" t="s">
-        <v>417</v>
+        <v>390</v>
       </c>
       <c r="K38" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="L38" t="s">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="M38" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="N38" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="O38" t="s">
-        <v>70</v>
+        <v>393</v>
       </c>
       <c r="P38" t="s">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="T38" t="s">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="U38" t="s">
-        <v>422</v>
+        <v>395</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -4026,55 +4050,55 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>423</v>
+        <v>396</v>
       </c>
       <c r="C39" t="s">
-        <v>424</v>
+        <v>397</v>
       </c>
       <c r="D39">
         <v>2025</v>
       </c>
       <c r="E39">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>425</v>
+        <v>398</v>
       </c>
       <c r="H39" t="s">
-        <v>426</v>
+        <v>399</v>
       </c>
       <c r="I39" t="s">
-        <v>427</v>
+        <v>400</v>
       </c>
       <c r="J39" t="s">
-        <v>428</v>
+        <v>401</v>
       </c>
       <c r="K39" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="L39" t="s">
-        <v>429</v>
+        <v>402</v>
       </c>
       <c r="M39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N39" t="s">
-        <v>430</v>
+        <v>403</v>
       </c>
       <c r="O39" t="s">
-        <v>70</v>
+        <v>404</v>
       </c>
       <c r="P39" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="T39" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="U39" t="s">
-        <v>433</v>
+        <v>407</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4082,55 +4106,55 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="C40" t="s">
-        <v>435</v>
+        <v>409</v>
       </c>
       <c r="D40">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G40" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="H40" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="I40" t="s">
-        <v>438</v>
+        <v>412</v>
       </c>
       <c r="J40" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
       <c r="K40" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="L40" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="M40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N40" t="s">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="O40" t="s">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="P40" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="T40" t="s">
-        <v>444</v>
+        <v>418</v>
       </c>
       <c r="U40" t="s">
-        <v>445</v>
+        <v>419</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -4138,55 +4162,55 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="C41" t="s">
-        <v>447</v>
+        <v>421</v>
       </c>
       <c r="D41">
         <v>2025</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F41">
         <v>2</v>
       </c>
       <c r="G41" t="s">
-        <v>448</v>
+        <v>422</v>
       </c>
       <c r="H41" t="s">
-        <v>449</v>
+        <v>423</v>
       </c>
       <c r="I41" t="s">
-        <v>450</v>
+        <v>424</v>
       </c>
       <c r="J41" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
       <c r="K41" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="L41" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="M41" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="N41" t="s">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="O41" t="s">
-        <v>453</v>
+        <v>428</v>
       </c>
       <c r="P41" t="s">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="T41" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="U41" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4194,55 +4218,55 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>456</v>
+        <v>432</v>
       </c>
       <c r="C42" t="s">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="D42">
         <v>2025</v>
       </c>
       <c r="E42">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="H42" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="I42" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="J42" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="K42" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="L42" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="M42" t="s">
-        <v>43</v>
+        <v>439</v>
       </c>
       <c r="N42" t="s">
-        <v>463</v>
+        <v>440</v>
       </c>
       <c r="O42" t="s">
-        <v>464</v>
+        <v>441</v>
       </c>
       <c r="P42" t="s">
-        <v>465</v>
+        <v>382</v>
       </c>
       <c r="T42" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="U42" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -4250,55 +4274,335 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="C43" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="D43">
         <v>2025</v>
       </c>
       <c r="E43">
+        <v>5</v>
+      </c>
+      <c r="F43">
+        <v>2</v>
+      </c>
+      <c r="G43" t="s">
+        <v>446</v>
+      </c>
+      <c r="H43" t="s">
+        <v>447</v>
+      </c>
+      <c r="I43" t="s">
+        <v>448</v>
+      </c>
+      <c r="J43" t="s">
+        <v>449</v>
+      </c>
+      <c r="K43" t="s">
+        <v>113</v>
+      </c>
+      <c r="L43" t="s">
+        <v>450</v>
+      </c>
+      <c r="M43" t="s">
+        <v>58</v>
+      </c>
+      <c r="N43" t="s">
+        <v>451</v>
+      </c>
+      <c r="O43" t="s">
+        <v>85</v>
+      </c>
+      <c r="P43" t="s">
+        <v>452</v>
+      </c>
+      <c r="T43" t="s">
+        <v>453</v>
+      </c>
+      <c r="U43" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>455</v>
+      </c>
+      <c r="C44" t="s">
+        <v>456</v>
+      </c>
+      <c r="D44">
+        <v>2025</v>
+      </c>
+      <c r="E44">
         <v>13</v>
       </c>
-      <c r="F43">
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44" t="s">
+        <v>457</v>
+      </c>
+      <c r="H44" t="s">
+        <v>458</v>
+      </c>
+      <c r="I44" t="s">
+        <v>459</v>
+      </c>
+      <c r="J44" t="s">
+        <v>460</v>
+      </c>
+      <c r="K44" t="s">
+        <v>113</v>
+      </c>
+      <c r="L44" t="s">
+        <v>461</v>
+      </c>
+      <c r="M44" t="s">
+        <v>58</v>
+      </c>
+      <c r="N44" t="s">
+        <v>462</v>
+      </c>
+      <c r="O44" t="s">
+        <v>85</v>
+      </c>
+      <c r="P44" t="s">
+        <v>463</v>
+      </c>
+      <c r="T44" t="s">
+        <v>464</v>
+      </c>
+      <c r="U44" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>466</v>
+      </c>
+      <c r="C45" t="s">
+        <v>467</v>
+      </c>
+      <c r="D45">
+        <v>2025</v>
+      </c>
+      <c r="E45">
+        <v>4</v>
+      </c>
+      <c r="F45">
+        <v>2</v>
+      </c>
+      <c r="G45" t="s">
+        <v>468</v>
+      </c>
+      <c r="H45" t="s">
+        <v>469</v>
+      </c>
+      <c r="I45" t="s">
+        <v>470</v>
+      </c>
+      <c r="J45" t="s">
+        <v>471</v>
+      </c>
+      <c r="K45" t="s">
+        <v>113</v>
+      </c>
+      <c r="L45" t="s">
+        <v>472</v>
+      </c>
+      <c r="M45" t="s">
+        <v>42</v>
+      </c>
+      <c r="N45" t="s">
+        <v>473</v>
+      </c>
+      <c r="O45" t="s">
+        <v>474</v>
+      </c>
+      <c r="P45" t="s">
+        <v>475</v>
+      </c>
+      <c r="T45" t="s">
+        <v>476</v>
+      </c>
+      <c r="U45" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>478</v>
+      </c>
+      <c r="C46" t="s">
+        <v>479</v>
+      </c>
+      <c r="D46">
+        <v>2025</v>
+      </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
+      <c r="F46">
+        <v>2</v>
+      </c>
+      <c r="G46" t="s">
+        <v>480</v>
+      </c>
+      <c r="H46" t="s">
+        <v>481</v>
+      </c>
+      <c r="I46" t="s">
+        <v>482</v>
+      </c>
+      <c r="J46" t="s">
+        <v>483</v>
+      </c>
+      <c r="K46" t="s">
+        <v>113</v>
+      </c>
+      <c r="L46" t="s">
+        <v>482</v>
+      </c>
+      <c r="M46" t="s">
+        <v>26</v>
+      </c>
+      <c r="N46" t="s">
+        <v>484</v>
+      </c>
+      <c r="O46" t="s">
+        <v>485</v>
+      </c>
+      <c r="P46" t="s">
+        <v>484</v>
+      </c>
+      <c r="T46" t="s">
+        <v>486</v>
+      </c>
+      <c r="U46" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>488</v>
+      </c>
+      <c r="C47" t="s">
+        <v>489</v>
+      </c>
+      <c r="D47">
+        <v>2025</v>
+      </c>
+      <c r="E47">
+        <v>13</v>
+      </c>
+      <c r="F47">
         <v>1</v>
       </c>
-      <c r="G43" t="s">
-        <v>458</v>
-      </c>
-      <c r="H43" t="s">
-        <v>459</v>
-      </c>
-      <c r="I43" t="s">
-        <v>470</v>
-      </c>
-      <c r="J43" t="s">
-        <v>471</v>
-      </c>
-      <c r="K43" t="s">
-        <v>41</v>
-      </c>
-      <c r="L43" t="s">
-        <v>462</v>
-      </c>
-      <c r="M43" t="s">
-        <v>43</v>
-      </c>
-      <c r="N43" t="s">
-        <v>472</v>
-      </c>
-      <c r="O43" t="s">
-        <v>464</v>
-      </c>
-      <c r="P43" t="s">
-        <v>472</v>
-      </c>
-      <c r="T43" t="s">
-        <v>473</v>
-      </c>
-      <c r="U43" t="s">
-        <v>467</v>
+      <c r="G47" t="s">
+        <v>490</v>
+      </c>
+      <c r="H47" t="s">
+        <v>491</v>
+      </c>
+      <c r="I47" t="s">
+        <v>492</v>
+      </c>
+      <c r="J47" t="s">
+        <v>493</v>
+      </c>
+      <c r="K47" t="s">
+        <v>56</v>
+      </c>
+      <c r="L47" t="s">
+        <v>494</v>
+      </c>
+      <c r="M47" t="s">
+        <v>58</v>
+      </c>
+      <c r="N47" t="s">
+        <v>495</v>
+      </c>
+      <c r="O47" t="s">
+        <v>496</v>
+      </c>
+      <c r="P47" t="s">
+        <v>497</v>
+      </c>
+      <c r="T47" t="s">
+        <v>498</v>
+      </c>
+      <c r="U47" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>500</v>
+      </c>
+      <c r="C48" t="s">
+        <v>501</v>
+      </c>
+      <c r="D48">
+        <v>2025</v>
+      </c>
+      <c r="E48">
+        <v>13</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48" t="s">
+        <v>490</v>
+      </c>
+      <c r="H48" t="s">
+        <v>491</v>
+      </c>
+      <c r="I48" t="s">
+        <v>502</v>
+      </c>
+      <c r="J48" t="s">
+        <v>503</v>
+      </c>
+      <c r="K48" t="s">
+        <v>56</v>
+      </c>
+      <c r="L48" t="s">
+        <v>494</v>
+      </c>
+      <c r="M48" t="s">
+        <v>58</v>
+      </c>
+      <c r="N48" t="s">
+        <v>504</v>
+      </c>
+      <c r="O48" t="s">
+        <v>496</v>
+      </c>
+      <c r="P48" t="s">
+        <v>504</v>
+      </c>
+      <c r="T48" t="s">
+        <v>505</v>
+      </c>
+      <c r="U48" t="s">
+        <v>499</v>
       </c>
     </row>
   </sheetData>
